--- a/Разбираемся с артефактом в монте-карло.xlsx
+++ b/Разбираемся с артефактом в монте-карло.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13440"/>
+    <workbookView windowWidth="25600" windowHeight="10400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,11 +115,40 @@
       </xdr:spPr>
     </xdr:pic>
   </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_9DABEB45087C45F4B82CF20FFFEB6BAA"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14582775" y="2501900"/>
+          <a:ext cx="15478125" cy="9363075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
 </etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>№</t>
   </si>
@@ -161,6 +190,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">то же самое </t>
   </si>
   <si>
     <t>только с внешней границы (исходной)</t>
@@ -176,7 +208,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,13 +226,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -669,156 +694,159 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -828,7 +856,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1149,47 +1179,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23.5"/>
   <cols>
-    <col min="1" max="3" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8888888888889" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="99.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="8" width="20.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="38.2222222222222" customWidth="1"/>
-    <col min="10" max="21" width="13.6666666666667" customWidth="1"/>
+    <col min="1" max="3" width="13.6636363636364" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.8909090909091" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.4454545454545" style="2" customWidth="1"/>
+    <col min="6" max="6" width="99.5545454545454" style="2" customWidth="1"/>
+    <col min="7" max="8" width="20.8909090909091" customWidth="1"/>
+    <col min="9" max="9" width="38.2181818181818" customWidth="1"/>
+    <col min="10" max="21" width="13.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="69" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="69" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="66" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="66" customHeight="1" spans="1:9">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1199,25 +1229,25 @@
       <c r="C2" s="4">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="5" t="str">
         <f>_xlfn.DISPIMG("ID_C0976ACD7C3B4D8EA674BFCBED9FC749",1)</f>
         <v>=DISPIMG("ID_C0976ACD7C3B4D8EA674BFCBED9FC749",1)</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="62" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="62" customHeight="1" spans="1:9">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -1227,13 +1257,13 @@
       <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="5" t="str">
@@ -1244,9 +1274,11 @@
         <f>_xlfn.DISPIMG("ID_010BDF85D43643C0B87DAF1CD45850ED",1)</f>
         <v>=DISPIMG("ID_010BDF85D43643C0B87DAF1CD45850ED",1)</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" ht="67" customHeight="1" spans="1:9">
+    <row r="4" s="1" customFormat="1" ht="67" customHeight="1" spans="1:9">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -1256,117 +1288,122 @@
       <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5" t="str">
+        <f>_xlfn.DISPIMG("ID_9DABEB45087C45F4B82CF20FFFEB6BAA",1)</f>
+        <v>=DISPIMG("ID_9DABEB45087C45F4B82CF20FFFEB6BAA",1)</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
     </row>
-    <row r="5" ht="36" customHeight="1" spans="1:9">
+    <row r="5" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
-    <row r="6" ht="36" customHeight="1" spans="1:9">
+    <row r="6" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
-    <row r="7" ht="36" customHeight="1" spans="1:9">
+    <row r="7" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:9">
+    <row r="8" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
     </row>
-    <row r="9" ht="36" customHeight="1" spans="1:9">
+    <row r="9" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
     </row>
-    <row r="11" ht="36" customHeight="1" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
-    <row r="12" ht="36" customHeight="1" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
-    <row r="13" ht="36" customHeight="1" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="36" customHeight="1" spans="1:9">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" ht="36" customHeight="1"/>
     <row r="15" ht="36" customHeight="1"/>
